--- a/src/attributions/attributions_ig_traj_128.xlsx
+++ b/src/attributions/attributions_ig_traj_128.xlsx
@@ -1568,22 +1568,22 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.08791191509767822</v>
+        <v>-0.1069965275093066</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3652384717648946</v>
+        <v>0.004232047586125578</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2396541464402712</v>
+        <v>0.01974809800475606</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1592,25 +1592,25 @@
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08537322396548806</v>
+        <v>-0.06754081216755212</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1239990704453165</v>
+        <v>0.01449307260581185</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07654635198438114</v>
+        <v>-0.008964369180273716</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -1622,22 +1622,22 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.03452832533437529</v>
+        <v>-0.02771509793202837</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2504893028765973</v>
+        <v>0.02224136231608616</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1245368472501413</v>
+        <v>-0.02747534257227106</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1649,25 +1649,25 @@
         <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.08839588270590031</v>
+        <v>0.08046478000541057</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.02599812769913906</v>
+        <v>0.004213123818428344</v>
       </c>
       <c r="AE3" t="n">
         <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.06597689992627845</v>
+        <v>-0.07651574929182108</v>
       </c>
       <c r="AG3" t="n">
         <v>-0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1676,127 +1676,127 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02437204485091017</v>
+        <v>-0.05725615578464914</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.1129339502583718</v>
+        <v>0.02803221556068364</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.09366500658296256</v>
+        <v>-0.2063366334501232</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
         <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.05915053257121387</v>
+        <v>-0.1288420305233891</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3192179136651396</v>
+        <v>0.04226220431766461</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.5169386104930795</v>
+        <v>-0.2020285115856235</v>
       </c>
       <c r="AY3" t="n">
         <v>-0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.1917204755376496</v>
+        <v>0.03383296431087932</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.09872791696019362</v>
+        <v>-0.01514523828209801</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.006941535062423008</v>
+        <v>0.2563674409843623</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.04835628181753571</v>
+        <v>0.01163894107465676</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.2854305221469292</v>
+        <v>0.04226150530128584</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2526280480221357</v>
+        <v>-0.02741460101574639</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.007786482781398975</v>
+        <v>-0.08323133456709503</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.09265800225158566</v>
+        <v>0.06689019611414816</v>
       </c>
       <c r="BX3" t="n">
         <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.4369604062011576</v>
+        <v>-0.07726480456953658</v>
       </c>
       <c r="BZ3" t="n">
         <v>-0</v>
@@ -1811,19 +1811,19 @@
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.008511171944066139</v>
+        <v>0.03183702211370056</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.08010125009402917</v>
+        <v>0.008686958878829285</v>
       </c>
       <c r="CG3" t="n">
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.08164925740652436</v>
+        <v>0.03125505949735131</v>
       </c>
       <c r="CI3" t="n">
         <v>0</v>
@@ -1832,31 +1832,31 @@
         <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.02229970839259613</v>
+        <v>-0.01937701674793772</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1354062139262281</v>
+        <v>-0.04784071624256465</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.4500000834416313</v>
+        <v>-0.01736400694842873</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
         <v>-0</v>
@@ -1865,19 +1865,19 @@
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.01587143813837826</v>
+        <v>0.03923928487734069</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.05250876139995658</v>
+        <v>0.01287198738417202</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.008322234153447973</v>
+        <v>0.01567632506567514</v>
       </c>
       <c r="DA3" t="n">
         <v>-0</v>
@@ -1886,55 +1886,55 @@
         <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0590727920587358</v>
+        <v>0.034489879486417</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.00498859946268629</v>
+        <v>0.0007208293308080359</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.1614417890626763</v>
+        <v>0.1968982306974276</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.2856152664897854</v>
+        <v>0.1038984989833552</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.04503199957650542</v>
+        <v>-0.02408443990009523</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.1739695312280433</v>
+        <v>0.09381525845268986</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
         <v>0</v>
@@ -1943,49 +1943,49 @@
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.1078502800891281</v>
+        <v>0.1112590852238341</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.1033759884523719</v>
+        <v>-0.04519953378707992</v>
       </c>
       <c r="DZ3" t="n">
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.1472334992593927</v>
+        <v>0.1560947664020471</v>
       </c>
       <c r="EB3" t="n">
         <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.08618019697294174</v>
+        <v>-0.08097700130684757</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.2066990331694972</v>
+        <v>0.01267892971415487</v>
       </c>
       <c r="EI3" t="n">
         <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.01643869367855903</v>
+        <v>0.09552461792634356</v>
       </c>
       <c r="EK3" t="n">
         <v>-0</v>
@@ -1994,55 +1994,55 @@
         <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN3" t="n">
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.1773167831098153</v>
+        <v>-0.03994275816423205</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.04739366264163417</v>
+        <v>-0.01092067472705097</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.2330251890355333</v>
+        <v>0.05089979608504369</v>
       </c>
       <c r="ET3" t="n">
         <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.0357864168045094</v>
+        <v>0.02045776316343222</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.05711825812381189</v>
+        <v>0.001163649726799557</v>
       </c>
       <c r="FA3" t="n">
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.02618076783266718</v>
+        <v>0.03183324940145438</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
         <v>-0</v>
@@ -2051,25 +2051,25 @@
         <v>0</v>
       </c>
       <c r="FF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.007079581701270169</v>
+        <v>0.1649330585138875</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0.01342359636414953</v>
+        <v>-0.001265330197015089</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.1236269385948111</v>
+        <v>0.01015957637257621</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
@@ -2081,19 +2081,19 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.00236744191515991</v>
+        <v>0.1520507956700643</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0.002079961452376161</v>
+        <v>0.0001045867077951501</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.004609126219167209</v>
+        <v>-0.003481873101495895</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2108,22 +2108,22 @@
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.03535355530336528</v>
+        <v>0.03615995326772532</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1078957581187904</v>
+        <v>0.01435496367566057</v>
       </c>
       <c r="GB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>-0</v>
@@ -2132,7 +2132,7 @@
         <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,22 +2140,22 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8710394671631164</v>
+        <v>0.6705747179872197</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3466994843504567</v>
+        <v>-0.3906673099064782</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02592194865264628</v>
+        <v>-0.1225136731613103</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -2167,19 +2167,19 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4556444676248363</v>
+        <v>0.5300100511917574</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2224351465869572</v>
+        <v>-0.3157299958509544</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.08688081622108408</v>
+        <v>-0.09889393031444048</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -2191,28 +2191,28 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2386168400308899</v>
+        <v>0.08408191365048885</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004706592326065299</v>
+        <v>-0.06106338403407045</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03525177933438636</v>
+        <v>-0.1228536948445256</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -2221,22 +2221,22 @@
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1816170357256561</v>
+        <v>-0.02499829361418145</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.07097230722584086</v>
+        <v>-0.06341750491099152</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.05676396467140446</v>
+        <v>-0.05949087577266851</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2245,25 +2245,25 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1130784868498021</v>
+        <v>0.2778072571375025</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.04611827837150441</v>
+        <v>-0.1215308051776594</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01659681675032569</v>
+        <v>0.1146710313206495</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
@@ -2275,43 +2275,43 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.610078158210688</v>
+        <v>0.4596427019408388</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.06485592075789547</v>
+        <v>-0.2758222261430718</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.2253918209457476</v>
+        <v>-0.2249534787215646</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1174423432048983</v>
+        <v>-0.05200349800384588</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.1755382247389391</v>
+        <v>-0.0231670730933985</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.3254139257698298</v>
+        <v>-0.01370526857715208</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,31 +2320,31 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.09883948564861393</v>
+        <v>-0.05180079263809485</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.08281640346023919</v>
+        <v>0.06481541940084042</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.04604402312203675</v>
+        <v>0.07711034222552116</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,22 +2356,22 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.4249048660377459</v>
+        <v>0.4490208970663647</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0.0163943715699826</v>
+        <v>-0.3889723937857873</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.05227530519769653</v>
+        <v>-0.1019100859562253</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
@@ -2383,46 +2383,46 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.1722846603082942</v>
+        <v>-0.2469918516059376</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0522259966257269</v>
+        <v>0.2734497995069168</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.0616690809212305</v>
+        <v>0.008670809848397061</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.04771695902637367</v>
+        <v>-0.2675468221583858</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.1195011580089848</v>
+        <v>0.2234860531135139</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.2081288149867093</v>
+        <v>0.0196201822049793</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2437,22 +2437,22 @@
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.1504121897238372</v>
+        <v>-0.2469600484582632</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.1031286187377086</v>
+        <v>0.2967494000297555</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.08131797883495366</v>
+        <v>0.02524242196945832</v>
       </c>
       <c r="DA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
@@ -2464,22 +2464,22 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.08800648742230996</v>
+        <v>-0.138073320545751</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.00403685740341776</v>
+        <v>-0.01283717324116516</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.0008672286362950778</v>
+        <v>0.002211658976162895</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.1167725323986862</v>
+        <v>-0.1502130938076757</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.01262838413707638</v>
+        <v>0.09092612320094585</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.08832718192617835</v>
+        <v>-0.02181132932645859</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
@@ -2518,22 +2518,22 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.09147843942486768</v>
+        <v>0.04636324577081082</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.04346785307112511</v>
+        <v>0.09793356435968882</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.11933987994309</v>
+        <v>0.006380601571175057</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
         <v>0</v>
@@ -2545,22 +2545,22 @@
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.07438680506875948</v>
+        <v>-0.1979483741705712</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.1328155425446202</v>
+        <v>0.2277006969642579</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.0132331647124434</v>
+        <v>0.03775070399413175</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
         <v>-0</v>
@@ -2569,25 +2569,25 @@
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.130351048731169</v>
+        <v>-0.1328869706711436</v>
       </c>
       <c r="EQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.0993126960383089</v>
+        <v>-0.231233180696917</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.08619733833051732</v>
+        <v>0.03194988379360439</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2596,49 +2596,49 @@
         <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.1587870425906422</v>
+        <v>-0.2778531485745068</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.08461662330145463</v>
+        <v>0.304724580826998</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.07397484186661744</v>
+        <v>-0.004139953360260129</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.00306564297489327</v>
+        <v>-0.1531958738980005</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.120156663262097</v>
+        <v>0.1545360673611549</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.05823557475915377</v>
+        <v>-0.06849825435544032</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.006681313895965726</v>
+        <v>0.00462576912273847</v>
       </c>
       <c r="FR4" t="n">
         <v>0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.01603093088226933</v>
+        <v>0.2469147695361011</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0001747851858335074</v>
+        <v>-0.001230077763406175</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2677,22 +2677,22 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02983010965216977</v>
+        <v>-0.1959878755295059</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.1008859144563786</v>
+        <v>0.1601923107442923</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
@@ -2701,7 +2701,7 @@
         <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,7 +2709,7 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.2425791943602417</v>
+        <v>-0.2160553333007874</v>
       </c>
       <c r="C5" t="n">
         <v>-0</v>
@@ -2718,13 +2718,13 @@
         <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03948961367028365</v>
+        <v>-0.01783481252462431</v>
       </c>
       <c r="F5" t="n">
-        <v>1.039424316288835</v>
+        <v>0.1859526129919176</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.04876372077303414</v>
+        <v>-0.06040028043171943</v>
       </c>
       <c r="L5" t="n">
         <v>-0</v>
@@ -2745,25 +2745,25 @@
         <v>-0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.04578065996010378</v>
+        <v>0.05115982155710832</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6648962914560094</v>
+        <v>0.1148715983430551</v>
       </c>
       <c r="P5" t="n">
         <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R5" t="n">
         <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04445264007489063</v>
+        <v>-0.09214741537039969</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
@@ -2772,10 +2772,10 @@
         <v>-0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1390882623365663</v>
+        <v>0.1047027431739682</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09360199783974275</v>
+        <v>-0.006704127144803481</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -2787,22 +2787,22 @@
         <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.0862103142087717</v>
+        <v>0.01112247556382819</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.03746990187958665</v>
+        <v>0.1696684522393646</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.03834152391748481</v>
+        <v>0.04304999779027644</v>
       </c>
       <c r="AH5" t="n">
         <v>-0</v>
@@ -2811,28 +2811,28 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
         <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.05620125093308213</v>
+        <v>-0.09145072731966115</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
         <v>-0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01401817233819889</v>
+        <v>-0.03197991141677461</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.1126852198399709</v>
+        <v>0.04846105826939198</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2841,22 +2841,22 @@
         <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.2629347926257324</v>
+        <v>-0.2893590892306165</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1799036171089354</v>
+        <v>0.1160119813565554</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.5507711793394763</v>
+        <v>0.06448073513571148</v>
       </c>
       <c r="AZ5" t="n">
         <v>-0</v>
@@ -2865,25 +2865,25 @@
         <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
         <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.1136806873328035</v>
+        <v>0.004026987100525575</v>
       </c>
       <c r="BE5" t="n">
         <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.03452265957999068</v>
+        <v>0.1028504274893385</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.2621497391275386</v>
+        <v>0.106129335064776</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         <v>-0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.2397711881079061</v>
+        <v>0.02661300794689079</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.03131023094121513</v>
+        <v>-0.01569514168188925</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.01368471781198003</v>
+        <v>0.02533318430197524</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,22 +2922,22 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.0880743442531438</v>
+        <v>-0.1780668989698319</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
         <v>-0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.09956395925869309</v>
+        <v>0.04887526248038233</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.3818101188557561</v>
+        <v>0.0710389361009503</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
@@ -2946,28 +2946,28 @@
         <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.03870547697756033</v>
+        <v>0.106488699730683</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02537038677676486</v>
+        <v>-0.001844119465899689</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.2223907145340299</v>
+        <v>-0.0532028608705827</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
@@ -2979,100 +2979,100 @@
         <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.005626666003567974</v>
+        <v>0.1194907587617229</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
         <v>0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.2433562690984757</v>
+        <v>-0.2008500896945821</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.01264746494787562</v>
+        <v>-0.08580392606222133</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
         <v>0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.01051940405543249</v>
+        <v>0.09885462672599458</v>
       </c>
       <c r="CX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.03557884242621811</v>
+        <v>-0.001416596784539403</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.2048391539333881</v>
+        <v>-0.05859470497000981</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.009761012824881137</v>
+        <v>0.02734012922666036</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.08434785283721197</v>
+        <v>0.119370099211321</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.006588519069676749</v>
+        <v>-0.01346616063252084</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.004119064919313392</v>
+        <v>0.03792316912281814</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ5" t="n">
         <v>-0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.01120694638042884</v>
+        <v>0.05118274904102198</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.08796481884652312</v>
+        <v>-0.03489221012497309</v>
       </c>
       <c r="DT5" t="n">
         <v>0</v>
@@ -3087,73 +3087,73 @@
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01758045352359271</v>
+        <v>-0.02704729899540759</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.04222218266670402</v>
+        <v>-0.02797011787568808</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.09562777014214743</v>
+        <v>-0.01441912648667387</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF5" t="n">
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.01244017546309478</v>
+        <v>0.06813424854378081</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.03211061675892096</v>
+        <v>0.03148163406611204</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.2016073966354616</v>
+        <v>-0.01227743812406574</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.009336922105905292</v>
+        <v>0.03643018860201736</v>
       </c>
       <c r="EQ5" t="n">
         <v>0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0756600225383291</v>
+        <v>0.01573090340990348</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.04595668011807464</v>
+        <v>-0.08300591933884517</v>
       </c>
       <c r="EU5" t="n">
         <v>-0</v>
@@ -3162,13 +3162,13 @@
         <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.008415352557052273</v>
+        <v>0.1106639176468086</v>
       </c>
       <c r="EZ5" t="n">
         <v>0</v>
@@ -3177,13 +3177,13 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.04482410350190383</v>
+        <v>0.01065302238187788</v>
       </c>
       <c r="FC5" t="n">
-        <v>-0.1910745444517064</v>
+        <v>-0.04775683995116156</v>
       </c>
       <c r="FD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3195,7 +3195,7 @@
         <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.05913748695129061</v>
+        <v>0.1161125531166826</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
@@ -3204,16 +3204,16 @@
         <v>0</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.006134047963538966</v>
+        <v>-0.07124531953681409</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0.1267632157242894</v>
+        <v>-0.08995716493999653</v>
       </c>
       <c r="FM5" t="n">
         <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
         <v>-0</v>
@@ -3222,7 +3222,7 @@
         <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.006160730989166677</v>
+        <v>-0.02169370360233233</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
@@ -3231,28 +3231,28 @@
         <v>0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.004849996316639962</v>
+        <v>0.0029689844741824</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0.2334307311742552</v>
+        <v>-0.04108385101933603</v>
       </c>
       <c r="FV5" t="n">
         <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.007105769839618132</v>
+        <v>0.09692515774869172</v>
       </c>
       <c r="GA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB5" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.01340827320199653</v>
+        <v>0.01353699661169776</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
@@ -3847,19 +3847,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2014250280682592</v>
+        <v>0.9336435119923314</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09200631829579886</v>
+        <v>0.1891344581343335</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.08062456975761953</v>
+        <v>-0.4634319324225969</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
@@ -3874,52 +3874,52 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1169314741976602</v>
+        <v>0.9337867684822142</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05743087201827</v>
+        <v>-0.1022455774342854</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.04369611145514982</v>
+        <v>-0.2365064978490205</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02952704333614772</v>
+        <v>0.1867991567780261</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.02979583603851226</v>
+        <v>-0.08914101262550274</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01735652581989239</v>
+        <v>0.06252024759630975</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>-0</v>
@@ -3928,7 +3928,7 @@
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03927605968392829</v>
+        <v>0.01696330619912315</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -3937,13 +3937,13 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02669298569573883</v>
+        <v>-0.3177397874669632</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.007339199732619318</v>
+        <v>-0.08275983957189997</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
@@ -3952,25 +3952,25 @@
         <v>-0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03651967162691664</v>
+        <v>0.1967576498169837</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01201795162506261</v>
+        <v>-0.07322698771022608</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.04574413505201786</v>
+        <v>-0.278815428178994</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3979,37 +3979,37 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1293526490807242</v>
+        <v>0.8106979718471371</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.03257341192550978</v>
+        <v>-0.2897166598462819</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.03328006498120321</v>
+        <v>-0.2706203243119994</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.03575674675821035</v>
+        <v>0.02284675125929471</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,70 +4018,70 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.05044775971662414</v>
+        <v>-0.086730941129772</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.01130037250511988</v>
+        <v>-0.2277943696046512</v>
       </c>
       <c r="BI7" t="n">
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.04839045177212065</v>
+        <v>0.1419268044432695</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.03335745530257225</v>
+        <v>0.1794775702816042</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.02025835431190887</v>
+        <v>0.1446443526131352</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.08692125659463283</v>
+        <v>0.6286152328161855</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.02838406756407246</v>
+        <v>-0.06768770401952547</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.003180392820273569</v>
+        <v>-0.1447493564073785</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>-0</v>
@@ -4090,7 +4090,7 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.03155980377962528</v>
+        <v>-0.2829813931652317</v>
       </c>
       <c r="CF7" t="n">
         <v>0</v>
@@ -4099,64 +4099,64 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.009172091426206265</v>
+        <v>0.01362375589936514</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.01876338434070613</v>
+        <v>0.152548192445982</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.002976341298522299</v>
+        <v>-0.4636140672760531</v>
       </c>
       <c r="CO7" t="n">
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.02266085058941829</v>
+        <v>0.3291538945744021</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.03165135832988876</v>
+        <v>0.1960929674672976</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.02430928672717448</v>
+        <v>-0.2954205202802397</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.00650877281200749</v>
+        <v>-0.06372920324723132</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0298776638715375</v>
+        <v>0.157872271056631</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
@@ -4168,22 +4168,22 @@
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.001680684392392846</v>
+        <v>0.01436450894135135</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02874136885777884</v>
+        <v>-0.07591485372028431</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0.001630632569430148</v>
+        <v>0.04902693049617071</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4192,31 +4192,31 @@
         <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.03208056501992437</v>
+        <v>-0.1863677507135232</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.03122569615192393</v>
+        <v>-0.07239628860875258</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.02934512895559011</v>
+        <v>0.1264332401981515</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
         <v>-0</v>
@@ -4225,19 +4225,19 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.00244316170148128</v>
+        <v>0.126444838025554</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.0330359396089983</v>
+        <v>-0.1169385883580768</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.01776810495189621</v>
+        <v>0.004610686532801153</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4249,28 +4249,28 @@
         <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.01651200922167229</v>
+        <v>-0.08808270468082749</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.01804569646023286</v>
+        <v>-0.1918142533988098</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.007079115459603778</v>
+        <v>0.06845124852703949</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,34 +4279,34 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.009539738808423888</v>
+        <v>-0.1179414742766615</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.007461725977477414</v>
+        <v>-0.1454742225429806</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.03341231867210454</v>
+        <v>-0.1355047883538932</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02148890221554492</v>
+        <v>-0.3047929322790603</v>
       </c>
       <c r="EZ7" t="n">
         <v>0</v>
@@ -4315,13 +4315,13 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.002581746181322266</v>
+        <v>-0.05915414286968453</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.02802274663835849</v>
+        <v>0.1272354977926765</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
@@ -4330,37 +4330,37 @@
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01692005645209731</v>
+        <v>-0.2083517112023294</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.05096335375462051</v>
+        <v>0.1357175060416868</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.01434206327597235</v>
+        <v>0.1327014232268958</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.003215376394661621</v>
+        <v>-0.1509295629654764</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,37 +4369,37 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.001729138103803006</v>
+        <v>-0.0008878248848073911</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.01769520306561963</v>
+        <v>-0.05005401664657584</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02782295327691912</v>
+        <v>-0.1942478836518023</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.02353871312291389</v>
+        <v>-0.0190101543056874</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
